--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -475,13 +475,13 @@
         <v>-0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>30.2</v>
+        <v>30.9</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="E2" t="n">
-        <v>33.7</v>
+        <v>34.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="D2" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="E2" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>34.3</v>
+        <v>35</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.5</v>
+        <v>30.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>34.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="D2" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="E2" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION.xlsx
+++ b/週五精準預測成果/FINAL_DECISION.xlsx
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C2" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="D2" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
